--- a/output/StructureDefinition-BRResultadoExameLaboratorial-3.2.1.xlsx
+++ b/output/StructureDefinition-BRResultadoExameLaboratorial-3.2.1.xlsx
@@ -14960,7 +14960,7 @@
         <v>79</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>78</v>
@@ -15077,7 +15077,7 @@
         <v>79</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>78</v>
@@ -15194,7 +15194,7 @@
         <v>79</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>78</v>
@@ -15779,7 +15779,7 @@
         <v>79</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>78</v>
@@ -15896,7 +15896,7 @@
         <v>79</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>78</v>
@@ -16013,7 +16013,7 @@
         <v>79</v>
       </c>
       <c r="G118" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H118" t="s" s="2">
         <v>78</v>
